--- a/output/pdf_financials_xlsx/DYG.xlsx
+++ b/output/pdf_financials_xlsx/DYG.xlsx
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>11.22637</v>
+        <v>-11.22637</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.365666</v>
+        <v>-0.365666</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.326325</v>
+        <v>-0.326325</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.126697</v>
+        <v>-1.126697</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.521547</v>
+        <v>-0.521547</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-0.292016</v>
@@ -1691,19 +1691,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>11.22637</v>
+        <v>-11.22637</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.365666</v>
+        <v>-0.365666</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.326325</v>
+        <v>-0.326325</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.126697</v>
+        <v>-1.126697</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.521547</v>
+        <v>-0.521547</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.292016</v>
@@ -1874,19 +1874,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>11.22637</v>
+        <v>-11.22637</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.365666</v>
+        <v>-0.365666</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.326325</v>
+        <v>-0.326325</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.126697</v>
+        <v>-1.126697</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.521547</v>
+        <v>-0.521547</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-0.292016</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-74.842467</v>
+        <v>74.842467</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -2148,19 +2148,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>11.22637</v>
+        <v>-11.22637</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.365666</v>
+        <v>-0.365666</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.326325</v>
+        <v>-0.326325</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.126697</v>
+        <v>-1.126697</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.521547</v>
+        <v>-0.521547</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.292016</v>
@@ -2270,19 +2270,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>11.22637</v>
+        <v>-11.22637</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.365666</v>
+        <v>-0.365666</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.326325</v>
+        <v>-0.326325</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.126697</v>
+        <v>-1.126697</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.521547</v>
+        <v>-0.521547</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.292016</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -6353,52 +6353,52 @@
         <v>2.218757</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.230241</v>
+        <v>4.448998</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.538312</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.652303</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.654109</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.654109</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.654109</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.654109</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.749557</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.891355</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.891355</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.891355</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.085504</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.170078</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.284044</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>3.584955</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>3.65722</v>
       </c>
     </row>
     <row r="93">
@@ -7927,46 +7927,46 @@
         <v>0.43187</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.0051</v>
+        <v>-0.03225</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.057958</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.010541</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0105</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.016927</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.012323</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.115</v>
+        <v>-0.018567</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.0425</v>
+        <v>-0.117437</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.167591</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.311251</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.243727</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-1.053717</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.765879</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0</v>
+        <v>-0.579761</v>
       </c>
     </row>
     <row r="119">
@@ -10064,7 +10064,11 @@
           <t>Share-based payment reserve (Notes 8 and 9)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -11882,7 +11886,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -13502,7 +13510,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -20206,7 +20218,11 @@
           <t>Share-based payment reserve 2,538,312</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -20518,7 +20534,11 @@
           <t>- - 66,085 - - 241,986 - - 11,484 Share- based payment reserve 2,230,241 2,538,312</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -23630,7 +23650,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -25118,7 +25142,11 @@
           <t>Exploration and evaluation asset costs and expenditures</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -26474,7 +26502,11 @@
           <t>Exploration and evaluation asset costs and expenditures</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -36277,10 +36309,10 @@
         </is>
       </c>
       <c r="H266" s="5" t="n">
-        <v>1.126697</v>
+        <v>-1.126697</v>
       </c>
       <c r="I266" s="5" t="n">
-        <v>0.521547</v>
+        <v>-0.521547</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -38382,13 +38414,13 @@
         </is>
       </c>
       <c r="E286" s="5" t="n">
-        <v>11.22637</v>
+        <v>-11.22637</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>0.365666</v>
+        <v>-0.365666</v>
       </c>
       <c r="G286" s="5" t="n">
-        <v>0.326325</v>
+        <v>-0.326325</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/DYG.xlsx
+++ b/output/pdf_financials_xlsx/DYG.xlsx
@@ -1131,58 +1131,58 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.024995</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00225</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00222</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.013302</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.016028</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.013576</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009341</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003827</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00235</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0008140000000000001</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002596</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002575</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000812</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000275</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007764</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.09890400000000001</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.113143</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.065438</v>
       </c>
     </row>
     <row r="13">
@@ -2148,58 +2148,58 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-11.22637</v>
+        <v>-11.201375</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.365666</v>
+        <v>-0.363416</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.326325</v>
+        <v>-0.324105</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.126697</v>
+        <v>-1.113395</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.521547</v>
+        <v>-0.5055190000000001</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.292016</v>
+        <v>-0.27844</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.310629</v>
+        <v>-0.301288</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.335583</v>
+        <v>-0.331756</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.215916</v>
+        <v>-0.213566</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.395218</v>
+        <v>-0.394404</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.415289</v>
+        <v>-0.412693</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.273509</v>
+        <v>-0.270934</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.18637</v>
+        <v>-0.185558</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.405431</v>
+        <v>-0.405156</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.20345</v>
+        <v>-0.195686</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.1945</v>
+        <v>-0.293404</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.484525</v>
+        <v>-0.597668</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-0.328053</v>
+        <v>-0.393491</v>
       </c>
     </row>
     <row r="28">
@@ -2270,58 +2270,58 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-11.22637</v>
+        <v>-11.201375</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.365666</v>
+        <v>-0.363416</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.326325</v>
+        <v>-0.324105</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.126697</v>
+        <v>-1.113395</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.521547</v>
+        <v>-0.5055190000000001</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.292016</v>
+        <v>-0.27844</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.310629</v>
+        <v>-0.301288</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.335583</v>
+        <v>-0.331756</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.215916</v>
+        <v>-0.213566</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.395218</v>
+        <v>-0.394404</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.415289</v>
+        <v>-0.412693</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.273509</v>
+        <v>-0.270934</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.18637</v>
+        <v>-0.185558</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.405431</v>
+        <v>-0.405156</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.20345</v>
+        <v>-0.195686</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.1945</v>
+        <v>-0.293404</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.484525</v>
+        <v>-0.597668</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.328053</v>
+        <v>-0.393491</v>
       </c>
     </row>
     <row r="30">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.025697</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.5729300000000001</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.5729300000000001</v>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.794557</v>
+        <v>0.820254</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.5729300000000001</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.5729300000000001</v>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.035596</v>
+        <v>0.009899</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.582969</v>
+        <v>0.010039</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.010039</v>
@@ -20960,7 +20960,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
@@ -32630,7 +32630,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -37888,7 +37888,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E281" s="5" t="n">

--- a/output/pdf_financials_xlsx/DYG.xlsx
+++ b/output/pdf_financials_xlsx/DYG.xlsx
@@ -836,28 +836,28 @@
         <v>0.145764</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.188928</v>
+        <v>0.207258</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.19184</v>
+        <v>0.206128</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.13747</v>
+        <v>0.147612</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.160314</v>
+        <v>0.176305</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.184306</v>
+        <v>0.197919</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.3972</v>
+        <v>0.450561</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.346275</v>
+        <v>0.371087</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.360961</v>
+        <v>0.386325</v>
       </c>
     </row>
     <row r="8">
@@ -7491,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000835</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -9014,7 +9014,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000835</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -9077,7 +9077,7 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.365789</v>
+        <v>-0.366624</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.21546</v>
@@ -24412,7 +24412,11 @@
           <t>Flow-through liability recognized on flow-through private placement $</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -29650,7 +29654,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -31670,7 +31678,11 @@
           <t>Director fees (Note 9)</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -31774,7 +31786,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
